--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Centri estivi e centri gioco.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Centri estivi e centri gioco.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="143">
   <si>
     <r>
       <t xml:space="preserve">
@@ -179,7 +179,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Vedi iscrizioni aperte</t>
+    <t>Consulta iscrizioni aperte</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -802,7 +802,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> per  l’anno </t>
+      <t xml:space="preserve"> per l’anno </t>
     </r>
     <r>
       <rPr>
@@ -1420,7 +1420,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è arrivata oltre il termine previsto dalla domanda di iscrizione. 
+      <t xml:space="preserve"> è arrivata oltre il termine previsto dalla domanda di iscrizione.
 </t>
     </r>
     <r>
@@ -1491,7 +1491,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Se hai già provveduto a pagare l'avviso ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.</t>
     </r>
@@ -1937,10 +1937,7 @@
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
-  </si>
-  <si>
-    <t>Vedi ricevuta</t>
+    <t>Vai alla ricevuta</t>
   </si>
   <si>
     <r>
@@ -1960,7 +1957,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -2070,14 +2067,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -2917,7 +2906,7 @@
         <v>108</v>
       </c>
       <c r="K6" s="34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L6" s="34" t="s">
         <v>108</v>
@@ -2929,12 +2918,12 @@
         <v>108</v>
       </c>
       <c r="O6" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>64</v>
@@ -2981,7 +2970,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>108</v>
@@ -3028,101 +3017,101 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="C9" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="34" t="s">
+      <c r="E9" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="F9" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="G9" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="H9" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="H9" s="34" t="s">
+      <c r="I9" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="J9" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="I9" s="34" t="s">
+      <c r="K9" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="L9" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="J9" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="K9" s="34" t="s">
+      <c r="M9" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="L9" s="34" t="s">
-        <v>124</v>
+      <c r="N9" s="34" t="s">
+        <v>125</v>
       </c>
-      <c r="M9" s="34" t="s">
+      <c r="O9" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="N9" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="O9" s="34" t="s">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="B10" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="C10" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="D10" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="E10" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="F10" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="G10" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="H10" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="H10" s="34" t="s">
+      <c r="I10" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="I10" s="34" t="s">
+      <c r="J10" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="J10" s="34" t="s">
+      <c r="K10" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="K10" s="34" t="s">
+      <c r="L10" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="L10" s="34" t="s">
+      <c r="M10" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="M10" s="34" t="s">
+      <c r="N10" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="N10" s="34" t="s">
-        <v>141</v>
-      </c>
       <c r="O10" s="34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>64</v>
@@ -3137,13 +3126,13 @@
         <v>64</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I11" s="34" t="s">
         <v>64</v>
